--- a/SORVEGLIANZA ACCESSI PS/Data_ILI.xlsx
+++ b/SORVEGLIANZA ACCESSI PS/Data_ILI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gianluigidantonio/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gianluigidantonio/Desktop/ILI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AF5B6F-036D-B64C-BC1E-1924F4F8CBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA8B185-F066-A74C-8FB0-2F530C517D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{03C12BC1-E631-2E48-8F98-0950F5557D40}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" activeTab="3" xr2:uid="{03C12BC1-E631-2E48-8F98-0950F5557D40}"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL ACCESS IN ER (REGION)" sheetId="1" r:id="rId1"/>
@@ -44,58 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="24">
-  <si>
-    <t>71. 933</t>
-  </si>
-  <si>
-    <t>73. 881</t>
-  </si>
-  <si>
-    <t>76. 057</t>
-  </si>
-  <si>
-    <t>77. 834</t>
-  </si>
-  <si>
-    <t>65. 074</t>
-  </si>
-  <si>
-    <t>62. 449</t>
-  </si>
-  <si>
-    <t>61. 739</t>
-  </si>
-  <si>
-    <t>63. 222</t>
-  </si>
-  <si>
-    <t>66. 040</t>
-  </si>
-  <si>
-    <t>65. 127</t>
-  </si>
-  <si>
-    <t>68. 265</t>
-  </si>
-  <si>
-    <t>67. 576</t>
-  </si>
-  <si>
-    <t>67. 025</t>
-  </si>
-  <si>
-    <t>69. 336</t>
-  </si>
-  <si>
-    <t>67. 927</t>
-  </si>
-  <si>
-    <t>68. 460</t>
-  </si>
-  <si>
-    <t>68. 929</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="7">
   <si>
     <t>WEEK</t>
   </si>
@@ -123,7 +72,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -217,12 +166,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +514,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="8">
         <v>2022</v>
@@ -608,8 +557,8 @@
       <c r="B3" s="10">
         <v>67.703000000000003</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>0</v>
+      <c r="C3" s="10">
+        <v>71.933000000000007</v>
       </c>
       <c r="D3" s="10">
         <v>69.856999999999999</v>
@@ -626,8 +575,8 @@
       <c r="B4" s="10">
         <v>63.091999999999999</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>1</v>
+      <c r="C4" s="10">
+        <v>73.881</v>
       </c>
       <c r="D4" s="10">
         <v>70.369</v>
@@ -644,8 +593,8 @@
       <c r="B5" s="10">
         <v>61.244999999999997</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>2</v>
+      <c r="C5" s="10">
+        <v>76.057000000000002</v>
       </c>
       <c r="D5" s="10">
         <v>70.945999999999998</v>
@@ -662,8 +611,8 @@
       <c r="B6" s="10">
         <v>63.396999999999998</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>3</v>
+      <c r="C6" s="10">
+        <v>77.834000000000003</v>
       </c>
       <c r="D6" s="10">
         <v>73.326999999999998</v>
@@ -680,8 +629,8 @@
       <c r="B7" s="10">
         <v>54.929000000000002</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>4</v>
+      <c r="C7" s="10">
+        <v>65.073999999999998</v>
       </c>
       <c r="D7" s="10">
         <v>68.742000000000004</v>
@@ -700,8 +649,8 @@
       <c r="B8" s="10">
         <v>51</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>5</v>
+      <c r="C8" s="10">
+        <v>62.448999999999998</v>
       </c>
       <c r="D8" s="10">
         <v>63.643999999999998</v>
@@ -720,8 +669,8 @@
       <c r="B9" s="10">
         <v>51.499000000000002</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>6</v>
+      <c r="C9" s="10">
+        <v>61.738999999999997</v>
       </c>
       <c r="D9" s="10">
         <v>64.608999999999995</v>
@@ -740,8 +689,8 @@
       <c r="B10" s="10">
         <v>52.308999999999997</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>7</v>
+      <c r="C10" s="10">
+        <v>63.222000000000001</v>
       </c>
       <c r="D10" s="10">
         <v>66.956999999999994</v>
@@ -760,8 +709,8 @@
       <c r="B11" s="10">
         <v>56.314999999999998</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>8</v>
+      <c r="C11" s="10">
+        <v>66.040000000000006</v>
       </c>
       <c r="D11" s="10">
         <v>69.034999999999997</v>
@@ -780,8 +729,8 @@
       <c r="B12" s="10">
         <v>58.052</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>9</v>
+      <c r="C12" s="10">
+        <v>65.126999999999995</v>
       </c>
       <c r="D12" s="10">
         <v>71.266000000000005</v>
@@ -800,8 +749,8 @@
       <c r="B13" s="10">
         <v>59.177999999999997</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>10</v>
+      <c r="C13" s="10">
+        <v>68.265000000000001</v>
       </c>
       <c r="D13" s="10">
         <v>70.475999999999999</v>
@@ -820,8 +769,8 @@
       <c r="B14" s="10">
         <v>61.393999999999998</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>11</v>
+      <c r="C14" s="10">
+        <v>67.575999999999993</v>
       </c>
       <c r="D14" s="10">
         <v>71.474999999999994</v>
@@ -840,8 +789,8 @@
       <c r="B15" s="10">
         <v>60.034999999999997</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>12</v>
+      <c r="C15" s="10">
+        <v>67.025000000000006</v>
       </c>
       <c r="D15" s="10">
         <v>70.19</v>
@@ -860,8 +809,8 @@
       <c r="B16" s="10">
         <v>61.204999999999998</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>13</v>
+      <c r="C16" s="10">
+        <v>69.335999999999999</v>
       </c>
       <c r="D16" s="10">
         <v>70.692999999999998</v>
@@ -880,8 +829,8 @@
       <c r="B17" s="10">
         <v>64.265000000000001</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>14</v>
+      <c r="C17" s="10">
+        <v>67.927000000000007</v>
       </c>
       <c r="D17" s="10">
         <v>74.807000000000002</v>
@@ -900,8 +849,8 @@
       <c r="B18" s="10">
         <v>67.194000000000003</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>15</v>
+      <c r="C18" s="10">
+        <v>68.459999999999994</v>
       </c>
       <c r="D18" s="10">
         <v>75.784999999999997</v>
@@ -920,8 +869,8 @@
       <c r="B19" s="10">
         <v>68.298000000000002</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>16</v>
+      <c r="C19" s="10">
+        <v>68.929000000000002</v>
       </c>
       <c r="D19" s="10">
         <v>69.319999999999993</v>
@@ -985,7 +934,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="12">
         <v>2022</v>
@@ -1408,10 +1357,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C1" s="8">
         <v>2022</v>
@@ -1431,7 +1380,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>48</v>
@@ -1452,7 +1401,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>49</v>
@@ -1473,7 +1422,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B4" s="8">
         <v>50</v>
@@ -1494,7 +1443,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B5" s="8">
         <v>51</v>
@@ -1515,7 +1464,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>52</v>
@@ -1536,7 +1485,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
@@ -1559,7 +1508,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B8" s="8">
         <v>2</v>
@@ -1582,7 +1531,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B9" s="8">
         <v>3</v>
@@ -1605,7 +1554,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B10" s="8">
         <v>4</v>
@@ -1628,7 +1577,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B11" s="8">
         <v>5</v>
@@ -1651,7 +1600,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B12" s="8">
         <v>6</v>
@@ -1674,7 +1623,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B13" s="8">
         <v>7</v>
@@ -1697,7 +1646,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B14" s="8">
         <v>8</v>
@@ -1720,7 +1669,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B15" s="8">
         <v>9</v>
@@ -1743,7 +1692,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B16" s="8">
         <v>10</v>
@@ -1766,7 +1715,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B17" s="8">
         <v>11</v>
@@ -1789,7 +1738,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B18" s="8">
         <v>12</v>
@@ -1812,7 +1761,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B19" s="8">
         <v>13</v>
@@ -1835,7 +1784,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B20" s="8">
         <v>14</v>
@@ -1858,7 +1807,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B21" s="8">
         <v>15</v>
@@ -1881,7 +1830,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B22" s="8">
         <v>48</v>
@@ -1902,7 +1851,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B23" s="8">
         <v>49</v>
@@ -1923,7 +1872,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B24" s="8">
         <v>50</v>
@@ -1944,7 +1893,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B25" s="8">
         <v>51</v>
@@ -1965,7 +1914,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B26" s="8">
         <v>52</v>
@@ -1986,7 +1935,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B27" s="8">
         <v>1</v>
@@ -2009,7 +1958,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B28" s="8">
         <v>2</v>
@@ -2032,7 +1981,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B29" s="8">
         <v>3</v>
@@ -2055,7 +2004,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B30" s="8">
         <v>4</v>
@@ -2078,7 +2027,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B31" s="8">
         <v>5</v>
@@ -2101,7 +2050,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B32" s="8">
         <v>6</v>
@@ -2124,7 +2073,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
@@ -2147,7 +2096,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B34" s="8">
         <v>8</v>
@@ -2170,7 +2119,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B35" s="8">
         <v>9</v>
@@ -2193,7 +2142,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B36" s="8">
         <v>10</v>
@@ -2216,7 +2165,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B37" s="8">
         <v>11</v>
@@ -2239,7 +2188,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B38" s="8">
         <v>12</v>
@@ -2262,7 +2211,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B39" s="8">
         <v>13</v>
@@ -2285,7 +2234,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B40" s="8">
         <v>14</v>
@@ -2308,7 +2257,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B41" s="8">
         <v>15</v>
@@ -2331,7 +2280,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B42" s="8">
         <v>48</v>
@@ -2352,7 +2301,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B43" s="8">
         <v>49</v>
@@ -2373,7 +2322,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B44" s="8">
         <v>50</v>
@@ -2394,7 +2343,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B45" s="8">
         <v>51</v>
@@ -2415,7 +2364,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B46" s="8">
         <v>52</v>
@@ -2436,7 +2385,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B47" s="8">
         <v>1</v>
@@ -2459,7 +2408,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B48" s="8">
         <v>2</v>
@@ -2482,7 +2431,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B49" s="8">
         <v>3</v>
@@ -2505,7 +2454,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B50" s="8">
         <v>4</v>
@@ -2528,7 +2477,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B51" s="8">
         <v>5</v>
@@ -2551,7 +2500,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B52" s="8">
         <v>6</v>
@@ -2574,7 +2523,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B53" s="8">
         <v>7</v>
@@ -2597,7 +2546,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B54" s="8">
         <v>8</v>
@@ -2620,7 +2569,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B55" s="8">
         <v>9</v>
@@ -2643,7 +2592,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B56" s="8">
         <v>10</v>
@@ -2666,7 +2615,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B57" s="8">
         <v>11</v>
@@ -2689,7 +2638,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B58" s="8">
         <v>12</v>
@@ -2712,7 +2661,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B59" s="8">
         <v>13</v>
@@ -2735,7 +2684,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B60" s="8">
         <v>14</v>
@@ -2758,7 +2707,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B61" s="8">
         <v>15</v>
@@ -2781,7 +2730,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B62" s="8">
         <v>48</v>
@@ -2802,7 +2751,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B63" s="8">
         <v>49</v>
@@ -2823,7 +2772,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B64" s="8">
         <v>50</v>
@@ -2844,7 +2793,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B65" s="8">
         <v>51</v>
@@ -2865,7 +2814,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B66" s="8">
         <v>52</v>
@@ -2886,7 +2835,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B67" s="8">
         <v>1</v>
@@ -2909,7 +2858,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B68" s="8">
         <v>2</v>
@@ -2932,7 +2881,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B69" s="8">
         <v>3</v>
@@ -2955,7 +2904,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B70" s="8">
         <v>4</v>
@@ -2978,7 +2927,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B71" s="8">
         <v>5</v>
@@ -3001,7 +2950,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B72" s="8">
         <v>6</v>
@@ -3024,7 +2973,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B73" s="8">
         <v>7</v>
@@ -3047,7 +2996,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B74" s="8">
         <v>8</v>
@@ -3070,7 +3019,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B75" s="8">
         <v>9</v>
@@ -3093,7 +3042,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B76" s="8">
         <v>10</v>
@@ -3116,7 +3065,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B77" s="8">
         <v>11</v>
@@ -3139,7 +3088,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B78" s="8">
         <v>12</v>
@@ -3162,7 +3111,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B79" s="8">
         <v>13</v>
@@ -3185,7 +3134,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B80" s="8">
         <v>14</v>
@@ -3208,7 +3157,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B81" s="8">
         <v>15</v>
@@ -3231,7 +3180,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B82" s="8">
         <v>48</v>
@@ -3252,7 +3201,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B83" s="8">
         <v>49</v>
@@ -3273,7 +3222,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B84" s="8">
         <v>50</v>
@@ -3294,7 +3243,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B85" s="8">
         <v>51</v>
@@ -3315,7 +3264,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B86" s="8">
         <v>52</v>
@@ -3336,7 +3285,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B87" s="8">
         <v>1</v>
@@ -3359,7 +3308,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B88" s="8">
         <v>2</v>
@@ -3382,7 +3331,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B89" s="8">
         <v>3</v>
@@ -3405,7 +3354,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B90" s="8">
         <v>4</v>
@@ -3428,7 +3377,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B91" s="8">
         <v>5</v>
@@ -3451,7 +3400,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B92" s="8">
         <v>6</v>
@@ -3474,7 +3423,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B93" s="8">
         <v>7</v>
@@ -3497,7 +3446,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B94" s="8">
         <v>8</v>
@@ -3520,7 +3469,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B95" s="8">
         <v>9</v>
@@ -3543,7 +3492,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B96" s="8">
         <v>10</v>
@@ -3566,7 +3515,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B97" s="8">
         <v>11</v>
@@ -3589,7 +3538,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B98" s="8">
         <v>12</v>
@@ -3612,7 +3561,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B99" s="8">
         <v>13</v>
@@ -3635,7 +3584,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B100" s="8">
         <v>14</v>
@@ -3658,7 +3607,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B101" s="8">
         <v>15</v>
@@ -3764,7 +3713,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7">
         <v>2022</v>
@@ -4187,7 +4136,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7">
         <v>2022</v>
@@ -4610,7 +4559,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7">
         <v>2022</v>
